--- a/documents/china_southern_air/南航订舱模版.xlsx
+++ b/documents/china_southern_air/南航订舱模版.xlsx
@@ -54,13 +54,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="21">
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>南航订舱模版</t>
     </r>
     <r>
@@ -71,7 +64,7 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-（注意：橙色列为必填项，灰色列为非必填项）</t>
+（注意：橙色列为必填项）</t>
     </r>
   </si>
   <si>
@@ -145,7 +138,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,10 +148,10 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -319,13 +312,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -337,7 +323,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -347,12 +333,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF88825"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.35"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,7 +670,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -714,16 +694,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
@@ -732,89 +712,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -831,9 +811,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1454,10 +1431,10 @@
       <c r="P2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1469,7 +1446,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="7"/>
+      <c r="D3" s="6"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -1482,7 +1459,7 @@
       <c r="N3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="8"/>
+      <c r="O3" s="7"/>
       <c r="P3" s="4" t="s">
         <v>20</v>
       </c>
@@ -1497,7 +1474,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="7"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -1510,7 +1487,7 @@
       <c r="N4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="8"/>
+      <c r="O4" s="7"/>
       <c r="P4" s="4" t="s">
         <v>20</v>
       </c>
@@ -1533,7 +1510,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -1546,7 +1523,7 @@
       <c r="N5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="8"/>
+      <c r="O5" s="7"/>
       <c r="P5" s="4" t="s">
         <v>20</v>
       </c>
@@ -1561,7 +1538,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="6"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -1574,7 +1551,7 @@
       <c r="N6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="8"/>
+      <c r="O6" s="7"/>
       <c r="P6" s="4" t="s">
         <v>20</v>
       </c>
@@ -1589,7 +1566,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="7"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -1602,7 +1579,7 @@
       <c r="N7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O7" s="8"/>
+      <c r="O7" s="7"/>
       <c r="P7" s="4" t="s">
         <v>20</v>
       </c>
@@ -1617,7 +1594,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="6"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -1630,7 +1607,7 @@
       <c r="N8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="8"/>
+      <c r="O8" s="7"/>
       <c r="P8" s="4" t="s">
         <v>20</v>
       </c>
@@ -1645,7 +1622,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="7"/>
+      <c r="D9" s="6"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -1658,7 +1635,7 @@
       <c r="N9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="8"/>
+      <c r="O9" s="7"/>
       <c r="P9" s="4" t="s">
         <v>20</v>
       </c>
@@ -1673,7 +1650,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -1686,7 +1663,7 @@
       <c r="N10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O10" s="8"/>
+      <c r="O10" s="7"/>
       <c r="P10" s="4" t="s">
         <v>20</v>
       </c>
@@ -1701,7 +1678,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -1714,7 +1691,7 @@
       <c r="N11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="8"/>
+      <c r="O11" s="7"/>
       <c r="P11" s="4" t="s">
         <v>20</v>
       </c>
@@ -1729,7 +1706,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -1742,7 +1719,7 @@
       <c r="N12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O12" s="8"/>
+      <c r="O12" s="7"/>
       <c r="P12" s="4" t="s">
         <v>20</v>
       </c>
@@ -1757,7 +1734,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="7"/>
+      <c r="D13" s="6"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -1770,7 +1747,7 @@
       <c r="N13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O13" s="8"/>
+      <c r="O13" s="7"/>
       <c r="P13" s="4" t="s">
         <v>20</v>
       </c>
@@ -1785,7 +1762,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="6"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -1798,7 +1775,7 @@
       <c r="N14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O14" s="8"/>
+      <c r="O14" s="7"/>
       <c r="P14" s="4" t="s">
         <v>20</v>
       </c>
@@ -1813,7 +1790,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="7"/>
+      <c r="D15" s="6"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -1826,7 +1803,7 @@
       <c r="N15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O15" s="8"/>
+      <c r="O15" s="7"/>
       <c r="P15" s="4" t="s">
         <v>20</v>
       </c>
@@ -1841,7 +1818,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="6"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -1854,7 +1831,7 @@
       <c r="N16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O16" s="8"/>
+      <c r="O16" s="7"/>
       <c r="P16" s="4" t="s">
         <v>20</v>
       </c>
@@ -1869,7 +1846,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -1882,7 +1859,7 @@
       <c r="N17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O17" s="8"/>
+      <c r="O17" s="7"/>
       <c r="P17" s="4" t="s">
         <v>20</v>
       </c>
@@ -1897,7 +1874,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="6"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -1910,7 +1887,7 @@
       <c r="N18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O18" s="8"/>
+      <c r="O18" s="7"/>
       <c r="P18" s="4" t="s">
         <v>20</v>
       </c>
@@ -1925,7 +1902,7 @@
         <v>19</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="6"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -1938,7 +1915,7 @@
       <c r="N19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O19" s="8"/>
+      <c r="O19" s="7"/>
       <c r="P19" s="4" t="s">
         <v>20</v>
       </c>
@@ -1953,7 +1930,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="6"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -1966,7 +1943,7 @@
       <c r="N20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O20" s="8"/>
+      <c r="O20" s="7"/>
       <c r="P20" s="4" t="s">
         <v>20</v>
       </c>
@@ -1981,7 +1958,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="6"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -1994,7 +1971,7 @@
       <c r="N21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O21" s="8"/>
+      <c r="O21" s="7"/>
       <c r="P21" s="4" t="s">
         <v>20</v>
       </c>
@@ -2009,7 +1986,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="6"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -2022,7 +1999,7 @@
       <c r="N22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O22" s="8"/>
+      <c r="O22" s="7"/>
       <c r="P22" s="4" t="s">
         <v>20</v>
       </c>
@@ -2037,7 +2014,7 @@
         <v>19</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="7"/>
+      <c r="D23" s="6"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -2050,7 +2027,7 @@
       <c r="N23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O23" s="8"/>
+      <c r="O23" s="7"/>
       <c r="P23" s="4" t="s">
         <v>20</v>
       </c>
@@ -2065,7 +2042,7 @@
         <v>19</v>
       </c>
       <c r="C24" s="4"/>
-      <c r="D24" s="7"/>
+      <c r="D24" s="6"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -2078,7 +2055,7 @@
       <c r="N24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O24" s="8"/>
+      <c r="O24" s="7"/>
       <c r="P24" s="4" t="s">
         <v>20</v>
       </c>
@@ -2090,23 +2067,23 @@
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3 F4:F24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F24">
       <formula1>"普货,普货促销,跨越货物,普通急件,普货优惠,普货特惠,普货备份"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3 G4:G24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G24">
       <formula1>"9000,0302,4329"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 M4:M24">
-      <formula1>"南航快运,南航标运"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3 P3 N4:N24 P4:P24">
-      <formula1>"否,是"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3 O4:O24">
-      <formula1>"GEN,XPS,ELI,PER,"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G25:G53">
       <formula1>"9000,0302"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M24">
+      <formula1>"南航快运,南航标运"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N24 P3:P24">
+      <formula1>"否,是"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O24">
+      <formula1>"GEN,XPS,ELI,PER,"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
